--- a/TestData/LV_TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/LV_TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0D52D8-DF14-4592-92B1-516B2ED7A05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E2AD77-DFB8-4558-BB12-7D409EA3EA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -345,7 +345,7 @@
     <t>Abrasive Form</t>
   </si>
   <si>
-    <t>Brian Miller</t>
+    <t>Jennie Stewart</t>
   </si>
 </sst>
 </file>
@@ -733,13 +733,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -747,7 +747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>99</v>
       </c>
@@ -771,42 +771,42 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3FF30-5810-42A4-B6D3-B7BD65EBF170}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
@@ -819,14 +819,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30953EE-CA2E-4F7C-B9BA-21629FCB862C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -837,7 +837,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -848,7 +848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -859,7 +859,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -870,7 +870,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -890,17 +890,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -913,17 +913,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -937,13 +937,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1398F625-8674-4D63-93D8-B47E3A580505}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -951,7 +951,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -959,10 +959,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J11" s="2"/>
     </row>
   </sheetData>
@@ -974,12 +974,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1171,16 +1171,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F94DFB-4724-4A5C-994B-DCCD1086734F}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1225,22 +1225,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4780488B-FFD3-40DA-A9C2-BC61B540B5CE}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -1253,14 +1253,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751812A8-ABA8-4232-9D81-14F299F55479}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1284,17 +1284,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7552AB4B-37A5-4D47-8C03-7FFC70E2819F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>

--- a/TestData/LV_TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/LV_TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E2AD77-DFB8-4558-BB12-7D409EA3EA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6287B97F-DE4D-486F-8A3E-0422D70BE85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -733,13 +733,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -747,7 +747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>99</v>
       </c>
@@ -771,42 +771,42 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3FF30-5810-42A4-B6D3-B7BD65EBF170}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
@@ -819,14 +819,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30953EE-CA2E-4F7C-B9BA-21629FCB862C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -837,7 +837,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -848,7 +848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -859,7 +859,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -870,7 +870,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -890,17 +890,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -913,17 +913,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -937,13 +937,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1398F625-8674-4D63-93D8-B47E3A580505}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -951,7 +951,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -959,10 +959,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J11" s="2"/>
     </row>
   </sheetData>
@@ -974,12 +974,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1171,16 +1171,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F94DFB-4724-4A5C-994B-DCCD1086734F}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1225,22 +1225,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4780488B-FFD3-40DA-A9C2-BC61B540B5CE}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -1253,14 +1253,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751812A8-ABA8-4232-9D81-14F299F55479}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1284,17 +1284,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7552AB4B-37A5-4D47-8C03-7FFC70E2819F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
